--- a/results/assistant_audit.xlsx
+++ b/results/assistant_audit.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Earlier runs that chose DeepSeek: before and after the speed work, and two local models.</t>
+          <t>Earlier runs that chose DeepSeek: after and before the speed work, and two local models. Listed best first; the order the runs were made in is in results/assistant_model_trials.csv.</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>1. DeepSeek, full profile, before the speed work</t>
+          <t>DeepSeek, full profile, after the speed work</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -11536,22 +11536,22 @@
         <v>18</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>14.5</v>
+        <v>5.9</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>145.4</v>
+        <v>13</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.179</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2. DeepSeek, full profile, after the speed work</t>
+          <t>DeepSeek, full profile, before the speed work</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -11576,22 +11576,22 @@
         <v>18</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>13</v>
+        <v>145.4</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>3. DeepSeek, compact profile (control)</t>
+          <t>DeepSeek, compact profile (control)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -11631,7 +11631,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>4. Gemma 4 26B, local, compact profile</t>
+          <t>Gemma 4 26B, local, compact profile</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -11671,7 +11671,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>5. Qwen3 14B, local, compact profile</t>
+          <t>Qwen3 14B, local, compact profile</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">

--- a/results/assistant_audit.xlsx
+++ b/results/assistant_audit.xlsx
@@ -13,8 +13,9 @@
     <sheet name="Chemistry questions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Refinement stages" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Stereo note A-B test" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Model history" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Development runs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Linker difference A-B test" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Model history" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Development runs" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -668,36 +669,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model history</t>
+          <t>Linker difference A-B test</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Earlier runs that chose DeepSeek: after and before the speed work, and two local models. Listed best first; the order the runs were made in is in results/assistant_model_trials.csv.</t>
+          <t>The linker question, three times per variant, side by side. Without a computed difference between chain lengths, the assistant called the small but real 0-vs-1-carbon difference (+0.18 pKi, 95% CI +0.04 to +0.31) 'not a real effect', from overlapping intervals and the single-measurement noise floor. With it, every answer read the step correctly. Adopted.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Model history</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Earlier runs that chose DeepSeek: after and before the speed work, and two local models. Listed best first; the order the runs were made in is in results/assistant_model_trials.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Development runs</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Every exploratory run made while refining the assistant, labelled.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Every chemistry category cleared the 90% bar set before the runs, so no chemistry-specialist model is needed alongside DeepSeek; where it was slow or wrong, the fix was a tool, not a model.</t>
         </is>
@@ -11441,6 +11454,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="120" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>The linker question, three times per variant, side by side. Without a computed difference between chain lengths, the assistant called the small but real 0-vs-1-carbon difference (+0.18 pKi, 95% CI +0.04 to +0.31) 'not a real effect', from overlapping intervals and the single-measurement noise floor. With it, every answer read the step correctly. Adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>By variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Reads the 0 vs 1 step correctly</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mean s</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Cost $</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A: means and intervals only</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>B: with the computed difference</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Every answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Tools used</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>find_linkers</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>## The linker-length trend (measured)
+I used `find_linkers` to count the number of **sp³ carbons between any aromatic atom and a terminal phenyl group** (0 = phenyl directly attached; 1 = a one-carbon "benzyl-type" chain, etc.). Molecules matched only *through* fused-ring atoms were excluded, because those are ring paths, not flexible chains.
+| Linker atoms (sp³ C) | n molecules | n papers | mean pKi (95% CI) | median pKi |
+|---|---|---|---|---|
+| 0 (direct biaryl) | 899 | 109 | 6.73 (6.67–6.80) | 6.66 |
+| 1 | 437 | 59 | 6.91 (6.80–7.02) | 6.68 |
+| 2 | 5 | 5 | 6.96 (5.81–8.11) | 6.54 |
+| 3 | 1 | 1 | 6.80 (no CI, n=1) | 6.80 |
+| 4–6 | 0 | 0 | — | — |
+**What the data show:** going from a directly attached phenyl (0 carbons) to a one-carbon spacer, the mean pKi rises by only ~0.18 units (6.73 → 6.91), and the medians are essentially identical (6.66 → 6.68). The 95% CIs just barely touch (6.67–6.80 vs 6.80–7.02), so this is **not a clearly different** change. Beyond one carbon there is essentially **no real data**: only 5 molecules at 2 carbons and 1 molecule at 3 carbons, so no trend longer than one atom can be claimed from this dataset.
+## How much to trust it
+- **The 0-vs-1 comparison is well sampled** (899 and 437 molecules, from 109 and 59 papers), so it's a reliable estimate of the *average* for these two, mixed sets. But the shift (~0.18 pKi) is **smaller than the ~0.54 pKi measurement-noise floor**, and the confidence intervals overlap — so the honest conclusion is "roughly flat, with maybe a tiny mean increase."
+- **Anything longer than one carbon is not trustworthy.** The 2- and 3-carbon points come from 1–5 papers and 1–5 molecules; their statistics reflect a few individual compounds, not a general linker-length relationship.
+- **Confounding is a real issue.** The search matched "any aromatic atom" as the core, so the 0-carbon set (biaryls) and the 1-carbon set (benzyl-type compounds) are **different chemical series**, not matched pairs. The small mean difference could easily reflect which scaffolds happen to be in each bucket rather than a true effect of adding one methylene. The mean being pulled up while the median barely moves suggests a few high-affinity outliers, not a uniform shift.
+If you want a cleaner answer, the right experiment is a **matched comparison within one scaffold** — e.g. `compare_molecules` on two compounds that differ only by inserting one CH₂ between an aromatic core and a phenyl. I can run that if you give me (or let me pick) a pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>find_linkers</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Using the linker-length tool (which counts only genuine flexible sp³ carbons outside any ring, and discards matches that run through fused-ring atoms), here is what the data actually shows for a phenyl group attached to an aromatic core:
+| Linker carbons | n (genuine) | n_papers | Mean pKi (95% CI) | Median pKi | Min–max |
+|---|---|---|---|---|---|
+| 0 (directly attached) | 899 | 109 | 6.73 (6.67–6.80) | 6.66 | 4.12–10.42 |
+| 1 (one CH₂) | 437 | 59 | 6.91 (6.80–7.02) | 6.68 | 4.51–9.92 |
+| 2 | 5 | 5 | 6.96 (5.81–8.11) | 6.54 | 6.08–8.43 |
+| 3 | 1 | 1 | 6.80 (not estimable) | 6.80 | 6.80 |
+| 4–8 | 0 | 0 | — | — | — |
+**The bottom line: there is no real trend to trust.** The only linkers with enough data to compare are 0 vs 1 carbon, and they are effectively the same: the mean rises by only ~0.18 pKi (6.73 → 6.91), and the 95% confidence intervals overlap, while the medians are nearly identical (6.66 vs 6.68). So adding one methylene between an aromatic ring and a phenyl does not clearly change CB2 binding in this dataset.
+**Why I'd distrust any "longer chain" story:**
+- The 2-carbon group is only **5 molecules from 5 papers**, with a CI spanning ~2.3 pKi units — essentially uninformative.
+- The 3-carbon group is a **single molecule from a single paper**, so its value reflects one compound, not a length trend.
+- There are **zero** genuine 4–8-carbon linkers, so nothing can be said about chains of that length.
+- These are also *different molecule sets from different papers* (109 vs 59 papers for 0 vs 1), so even the 0-vs-1 comparison is cross-series and confounded — the two groups differ in more than just the linker. A proper check would need matched pairs within the same scaffold (via `compare_molecules`), which the current comparison does not do.
+One technical caveat worth flagging: the tool also excluded ring-path-only matches (e.g. 33 at length 1, 16 at length 3) because those carbons sit inside fused rings, not in a flexible linker — so the counts above are the *genuine* linker molecules only.
+*Source: measured values from the curated ChEMBL CB2 dataset, via the linker-length SAR tool.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>find_linkers</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>## Measured trend (from the data)
+I asked the linker-SAR tool to count molecules where a **phenyl group (benzene)** is attached to an **aromatic atom** through a chain of sp³ carbons. Genuine flexible chains only (chain atoms outside every ring):
+| Linker length | n (genuine) | n papers | Mean pKi (95% CI) |
+|---|---|---|---|
+| 0 (directly attached) | 899 | 109 | 6.73 (6.67–6.80) |
+| 1 carbon | 437 | 59 | 6.91 (6.80–7.02) |
+| 2 carbons | 5 | 5 | 6.96 (5.81–8.11) |
+| 3 carbons | 1 | 1 | 6.80 (no interval — single molecule) |
+| 4–6 carbons | 0 | 0 | no data |
+**What this says:** there is a small apparent rise of about **0.18 pKi** going from directly attached → one-carbon linker, but the 95% confidence intervals overlap, so that difference is **not clearly distinguishable from noise** (repeat measurements already disagree by ~0.5 pKi). Beyond one carbon, the dataset essentially runs out: **5 molecules** with a two-carbon linker, **1 molecule** with three, and **zero** with four or more.
+## How much to trust it
+- **The 0 → 1 carbon comparison is the only one with real sample sizes** (899 vs 437 molecules, from 109 and 59 papers). It is reasonably well-powered in count, but it is **not a matched comparison** — the two buckets mix different scaffolds and chemical series, so the small difference could come from the series that happen to populate each bucket rather than from the linker itself. Treat it as a weak, confounded hint, not a causal SAR trend.
+- **Two carbons and beyond: do not trust any trend.** n = 5 (from 5 papers) with a CI spanning 5.81–8.11 is uninformative, and 3 carbons rests on a single molecule from a single paper. Four-carbon and longer aryl→phenyl chains are simply **absent** from this dataset.
+**Bottom line:** the data support at most "a one-carbon spacer gives similar or very slightly higher affinity than direct attachment, and the difference is within measurement noise." There is **no usable evidence** here about what happens as the chain grows to 2+ carbons — if that's the SAR you care about, this dataset can't answer it, and you'd want matched pairs within a single scaffold (e.g. via `compare_molecules`) or external data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>find_linkers</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>## Linker-length SAR: aromatic ring → phenyl
+I searched all 3,576 molecules for a phenyl group attached to any aromatic atom through a chain of sp³ carbons, counting only genuine flexible chains (chain atoms outside every ring; matches that ran through fused-ring atoms were excluded). Measured pKi values, from the data:
+| Linker carbons | Meaning | n molecules | n papers | Mean pKi (95% CI) | Change vs shorter |
+|---|---|---|---|---|---|
+| 0 | phenyl directly attached (biphenyl) | 899 | 109 | 6.73 (6.67–6.80) | — |
+| 1 | benzyl (–CH₂–) | 437 | 59 | 6.91 (6.80–7.02) | **+0.18 (+0.04 to +0.31)** |
+| 2 | phenethyl (–CH₂CH₂–) | 5 | 5 | 6.96 (5.81–8.11) | +0.04 (−0.62 to +0.84) |
+| 3 | –(CH₂)₃– | 1 | 1 | 6.80 | no interval estimable |
+| 4–8 | | 0 | 0 | no data | no data |
+## What the trend says
+There is **no meaningful "longer chain" trend** to report — because longer chains essentially don't exist in this dataset.
+- **0 → 1 carbon:** a small average affinity gain of +0.18 pKi (95% CI 0.04–0.31), i.e. roughly 1.5-fold lower Kᵢ on average. The interval excludes zero, so the group averages really differ. But the effect is small, and it is a *dataset-wide* average across many different chemical series.
+- **1 → 2 carbons:** no detectable difference (CI −0.62 to +0.84, and only 5 molecules).
+- **3+ carbons:** essentially no data — one molecule at 3 carbons and zero at 4–8.
+## How much to trust it
+- **The 0 vs 1 comparison is statistically solid** in the sense of sample size: 899 vs 437 molecules drawn from 109 and 59 papers. The +0.18 pKi difference is real as a dataset-wide statement.
+- **But it is confounded, not causal.** Different chemical series use different linkers, so this is a mixed comparison across chemotypes, not a controlled lengthening of the same molecule. I would not claim "adding a CH₂ improves binding" without a matched-pair check (same scaffold, compare_molecules).
+- **The 1 vs 2 comparison cannot be trusted:** 5 molecules from 5 papers, with a 95% CI spanning ~2.7 pKi units — wider than the entire effect being tested.
+- **No chain of 2+ carbons is populated enough to support SAR at all**, so any "lengthening improves/flattens" narrative beyond one carbon would be speculation.
+**Bottom line:** In this dataset, going from a directly attached phenyl to a benzyl group is associated with a small (~0.2 log unit) affinity increase, but that's the only step with enough data to assess, and it mixes different series. There is no evidence here about 2-, 3- or longer carbon spacers. If you have a specific scaffold in mind, I can run a matched comparison within that scaffold — that's the only way to turn this into a credible causal statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>find_linkers, group_composition, group_composition</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>## What the data show
+I looked specifically at molecules with a **benzene (phenyl) group attached to an aromatic ring through 0–8 sp³ carbons**, using the linker finder that counts only genuine flexible chains (excluding matches where the "chain" is actually part of a fused ring).
+| sp³ carbons in linker | Genuine molecules | Source papers | Mean pKi (95% CI) | Δ vs previous length (95% CI) |
+|---|---|---|---|---|
+| 0 (phenyl directly on ring) | 899 | 109 | 6.73 (6.67–6.80) | — |
+| 1 (benzyl-type) | 437 | 59 | 6.91 (6.80–7.02) | **+0.18 (0.04–0.31)** |
+| 2 | 5 | 5 | 6.96 (5.81–8.11) | +0.04 (−0.62 to 0.84) |
+| 3 | 1 | 1 | 6.80 (CI not estimable) | — |
+| 4–8 | 0 | — | — | — |
+**The takeaway: there is no real "longer chain" trend to see.** The dataset essentially only contains phenyl attached directly (0 carbons) or through one CH₂ (1 carbon). Going from 0 to 1 carbon gives a small but statistically real average increase of **+0.18 pKi** (95% CI 0.04–0.31) — the interval excludes zero, so the group averages genuinely differ. Beyond that, there are only 5 molecules with a 2-carbon linker and 1 with a 3-carbon linker, so nothing can be concluded about chains of 2 or more carbons. (For context, a 3-carbon "chain" was almost entirely fused-ring artefacts — 16 matches were excluded as ring-path-only, leaving 1 genuine molecule.)
+## How much to trust the 0→1 result
+- **Statistically real, but chemically tiny.** +0.18 pKi is roughly a 1.5-fold change in Ki. That's far smaller than the ~0.54 pKi disagreement between repeat lab measurements and the ~0.6 pKi model validation error, so for any individual compound it would be lost in noise. The averages across 899 vs 437 molecules are precise enough to detect it, but the *size* of the effect is negligible.
+- **Confounded by which series use which linker.** Neither bucket is dominated by one series: the direct-phenyl set's largest scaffold is only 5.6% of molecules (top three: 5.6%, 3.7%, 2.8%), and the 1-carbon set's largest is 12.8% (coumarin + benzene; next 6.7%, 5.1%). Both come from many papers (109 and 59), so they're not single-lab artefacts — but they *are* different mixtures of chemotypes. The +0.18 could reflect that slightly higher-affinity series happen to use benzyl linkers rather than an intrinsic linker effect.
+- **No matched-pair control exists here.** To attribute the change to the linker itself, you'd want the same scaffold with the phenyl swapped between direct and CH₂ attachment. That comparison isn't possible from these aggregate numbers.
+**Bottom line:** measured trend = direct → one-carbon linker gives a barely-detectable, statistically significant average boost (+0.18 pKi), and there is effectively **no data for 2+ carbon linkers** to support any "longer chain" claim. Treat the 0→1 effect as real but confounded and chemically minor; do not extend it to longer chains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>find_linkers</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>I ran the linker-length SAR tool on the whole dataset, counting genuine sp3-carbon chains between any aromatic atom and a terminal benzene/phenyl group (atoms inside fused rings are excluded, since those aren't linkers). Here's what the measured data show:
+| Linker carbons | Molecules (genuine chain) | Papers | Mean pKi (95% CI) | Change vs previous length |
+|---|---|---|---|---|
+| 0 (phenyl directly attached) | 899 | 109 | 6.73 (6.67–6.80) | — |
+| 1 (benzyl-type) | 437 | 59 | 6.91 (6.80–7.02) | +0.18 (0.04–0.31) |
+| 2 | 5 | 5 | 6.96 (5.81–8.11) | +0.04 (−0.62 to +0.84) |
+| 3 | 1 | 1 | 6.80 (no CI) | — |
+| 4–8 | 0 | 0 | — | — |
+**The trend, such as it is (measured):** going from a directly attached phenyl to a one-carbon (benzyl) linker gives a small average increase of about **+0.18 pKi** (95% CI +0.04 to +0.31). That interval excludes zero, so at the whole-dataset level the two averages are genuinely different. The medians, though, are essentially identical (6.66 vs 6.68), so the effect is driven by a subset of higher-affinity one-carbon examples rather than a uniform shift.
+**Beyond one carbon there is no real trend to see.** Only **5 molecules** have a genuine 2-carbon chain, **1 molecule** has a 3-carbon chain, and there are **zero** compounds with 4–8 carbons. The 2-carbon mean's confidence interval (5.81–8.11) is so wide it overlaps everything, and the 3-carbon point is a single compound from a single paper.
+**How much should you trust this?**
+- The 0→1 step is statistically real as a dataset average, but it's a **small effect (~0.2 pKi)** and it is **confounded by chemistry**: the 0-carbon group spans 109 papers and the 1-carbon group 59 papers, so this is not one controlled series varying only the linker. Which series happen to use direct vs benzyl attachment drives the number as much as the linker itself.
+- The 2- and 3-carbon results are **far too sparse to trust** (5 and 1 molecules, respectively) — no credible SAR conclusion about longer chains is possible from this dataset.
+- There is simply **no data** for linkers of 4+ carbons, so any claim about longer chains would be pure extrapolation.
+One technical note: the tool flagged 33, 4, 16, 10 and 3 molecules that would have been *falsely* counted as 1–5-carbon linkers if matched by a naive SMARTS pattern, because the carbon path runs through a fused ring. Those were excluded, so the numbers above reflect genuine flexible chains.
+**Bottom line:** the only supportable statement is that a one-carbon linker looks slightly (but not dramatically) better than direct attachment on average; everything longer is essentially unrepresented. If you want to test this properly, do a **matched comparison within a single scaffold** (same ring system, varying only the linker) — I can set that up with `compare_molecules` if you point me at a specific series.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11713,7 +12117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/results/assistant_audit.xlsx
+++ b/results/assistant_audit.xlsx
@@ -14,8 +14,9 @@
     <sheet name="Refinement stages" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Stereo note A-B test" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Linker difference A-B test" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Model history" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Development runs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Pattern check A-B test" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Model history" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Development runs" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -681,39 +682,438 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model history</t>
+          <t>Pattern check A-B test</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Earlier runs that chose DeepSeek: after and before the speed work, and two local models. Listed best first; the order the runs were made in is in results/assistant_model_trials.csv.</t>
+          <t>Functional-group questions with answers counted by RDKit, side by side without and with the pattern check (each SMARTS the LLM writes is matched against small reference molecules; the tool result warns when it matches more than one group and says 'Clean' when it matches one). Round 1: the LLM used named groups for most questions; Q5 was worded ambiguously and both variants read it the same other way (reworded since). Without the check, a loose amide pattern counted ureas and carbamates (Q13: 1,693 for 1,572) and nothing flagged it; with it, the error was caught. Rounds 2-3 fixed over-refinement after a warning and checked each part of an 'A.B' pattern. Remaining misses in both variants are narrower definitions (acyl hydrazides as amides, sulfamides as sulfonamides), not loose patterns. Adopted.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Model history</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Earlier runs that chose DeepSeek: after and before the speed work, and two local models. Listed best first; the order the runs were made in is in results/assistant_model_trials.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Development runs</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Every exploratory run made while refining the assistant, labelled.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Every chemistry category cleared the 90% bar set before the runs, so no chemistry-specialist model is needed alongside DeepSeek; where it was slow or wrong, the fix was a tool, not a model.</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Question set</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Time of day</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Asked</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Mean s</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Median s</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Slowest s</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Cost $</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Bare: DeepSeek alone, first 11 chemistry questions (stopped; 120 s limit)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>chemistry</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Dataset A: pre-fetch off</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.078</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Dataset B: pre-fetch on</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Dataset E: pre-fetch on, thinking off</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.083</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry C: pre-fetch off, no R/S tool (stopped after 16)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>chemistry</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.413</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry D: pre-fetch on, no R/S tool</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>chemistry</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>R/S questions: R/S tool, pre-fetch on</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>chemistry</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>afternoon</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>R/S questions: R/S tool, pre-fetch off</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>chemistry</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>afternoon</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Bare smoke test: 20 s time limit</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>chemistry</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.011</v>
       </c>
     </row>
   </sheetData>
@@ -11845,6 +12245,2637 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Functional-group questions with answers counted by RDKit, side by side without and with the pattern check (each SMARTS the LLM writes is matched against small reference molecules; the tool result warns when it matches more than one group and says 'Clean' when it matches one). Round 1: the LLM used named groups for most questions; Q5 was worded ambiguously and both variants read it the same other way (reworded since). Without the check, a loose amide pattern counted ureas and carbamates (Q13: 1,693 for 1,572) and nothing flagged it; with it, the error was caught. Rounds 2-3 fixed over-refinement after a warning and checked each part of an 'A.B' pattern. Remaining misses in both variants are narrower definitions (acyl hydrazides as amides, sulfamides as sulfonamides), not loose patterns. Adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>By round and variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Warned</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mean s</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Cost $</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1. All 20 questions, first version</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A: no check</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>18/20</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1. All 20 questions, first version</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>B: pattern check</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>18/20</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2. Q13 and Q15 three times, with the 'Clean' status</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A: no check</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2. Q13 and Q15 three times, with the 'Clean' status</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>B: pattern check</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.139</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>3. Q15 three times, each part of an A.B pattern checked (adopted)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>A: no check</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>3. Q15 three times, each part of an A.B pattern checked (adopted)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>B: pattern check</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Every answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Warned</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Patterns the LLM sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a carboxylic acid group?</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>carboxylic_acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain an ester group?</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>ester</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a urea group?</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>urea</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a carbamate group?</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>carbamate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain a sulfone (not counting sulfonamides)?</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>sulfone | sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a nitrile?</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>nitrile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a ketone?</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>423</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>423</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>ketone</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a phenol (an OH directly on an aromatic ring)?</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>528</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>528</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>phenol</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain an aliphatic alcohol (an OH on an sp3 carbon)?</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>393</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>393</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>[CX4][OX2H] | hydroxyl | phenol | hydroxyl | phenol</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules have an NH2 attached directly to an aromatic ring, as in aniline?</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>[NH2][a]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules have an aliphatic primary amine (an NH2 on an sp3 carbon, not an amide)?</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>[NX3;H2;$(N[CX4]);!$(N[C,S]=[O,S])] | [NX3;H2][CX4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>1693</v>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>[NX3;H1;$(NC=[OX1])]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules have an alkyl aryl ether: an oxygen joining an aromatic ring to an sp3 carbon?</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1186</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>[a]-[O]-[CX4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>amide | sulfonamide | [NX3][CX3](=[OX1]).[NX3][SX4](=[OX1])(=[OX1]) | [NX3][CX3](=[OX1]) | [NX3][SX4](=[OX1])(=[OX1]) | [NX3][CX3](=[OX1])[#6] | [NX3][CX3](=[OX1])[#6].[NX3][SX4](=[OX1])(=[OX1])</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a carboxylic acid or an ester (either one)?</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>carboxylic_acid | ester | [CX3](=O)[OX2H1].[CX3](=O)[OX2][#6] | [$([CX3](=O)[OX2H1]),$([CX3](=O)[OX2][#6])] | [CX3](=O)[OX2H1].[CX3](=O)[OX2][#6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules with a carboxylic acid group?</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>6.747174079384505</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>6.747</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>carboxylic_acid | carboxylic_acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules with an ester but no carboxylic acid?</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>7.309807537614964</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>ester | ester | carboxylic_acid | ester | carboxylic_acid | ester | carboxylic_acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules containing a ketone?</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>7.4089353929735</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>7.409</v>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>ketone</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules containing a urea group?</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>6.417950030261713</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>urea</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a carboxylic acid group?</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>carboxylic_acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain an ester group?</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>ester</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a urea group?</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>urea</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a carbamate group?</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>carbamate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain a sulfone (not counting sulfonamides)?</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>sulfone | sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a nitrile?</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>nitrile</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a ketone?</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>423</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>423</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>ketone</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a phenol (an OH directly on an aromatic ring)?</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>528</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>528</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>phenol</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain an aliphatic alcohol (an OH on an sp3 carbon)?</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>393</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>393</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>[OX2H][CX4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules have an NH2 attached directly to an aromatic ring, as in aniline?</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>[NH2][a]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules have an aliphatic primary amine (an NH2 on an sp3 carbon, not an amide)?</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>[NX3;H2][CX4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>1477</v>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>[CX3](=O)[NX3;H1] | [CX3](=O)[NX3;H1][#6] | [CX3](=O)([#6,#1])[NX3;H1][#6] | [CX3](=O)([#6,#1])[NX3;H1][#6;!$(C=O)] | [CX3](=O)([#6,#1])[NX3;H1][#6;$(C=O)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules have an alkyl aryl ether: an oxygen joining an aromatic ring to an sp3 carbon?</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>1186</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>[a]-O-[CX4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>amide | sulfonamide | [CX3](=O)[NX3].[SX4](=O)(=O)[NX3] | [CX3](=O)[NX3] | [SX4](=O)(=O)[NX3] | [#6][CX3](=O)[NX3] | [CX3](=O)[NX3][#6] | [#6][CX3](=O)[NX3].[SX4](=O)(=O)[NX3] | [#6][CX3](=O)[NX3][SX4](=O)(=O)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a carboxylic acid or an ester (either one)?</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>carboxylic_acid | ester | carboxylic_acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules with a carboxylic acid group?</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>6.747174079384505</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>6.747</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>carboxylic_acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules with an ester but no carboxylic acid?</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>7.309807537614964</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>ester | carboxylic_acid | ester | carboxylic_acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules containing a ketone?</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>7.4089353929735</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>7.409</v>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>ketone</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>What is the median curated pKi of molecules containing a urea group?</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>6.417950030261713</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>6.418</v>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>urea</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>[CX3](=O)[NX3;H1] | amide | [CX3](=O)([#6])[NX3;H1] | [CX3](=O)([#6])[NX3] | [CX3](=O)([#6])[NX3;H2] | [CX3](=O)([#6])[NX3;H0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>amide | sulfonamide | [CX3](=O)[NX3].[SX4](=O)(=O)[NX3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>1693</v>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>[NX3;H1]C(=O)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>[#7][#6](=[#8]).[#7][#16](=[#8])(=[#8]) | amide | sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1693</v>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])[NX3H1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>[NX3][CX3](=[OX1]).[NX3][SX4](=[OX1])(=[OX1]) | [NX3][CX3](=[OX1])[#6].[SX4](=[OX1])(=[OX1])[NX3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>[NX3;H1;$(NC(=O))] | [#6][CX3](=O)[NX3;H1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])[NX3].[SX4](=[OX1])(=[OX1])[NX3] | amide | sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>1479</v>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>[#6][CX3](=O)[NX3;H1][#6] | [NX3;H1][CX3](=O)[#6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr"/>
+      <c r="I63" s="6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>[NX3][CX3](=[OX1])[#6].[SX4](=[OX1])(=[OX1])[NX3] | amide | sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain a secondary amide, i.e. an amide with an N-H?</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>1572</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
+      <c r="I64" s="6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>[NX3H1][CX3](=O)[#6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr"/>
+      <c r="I65" s="6" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>amide | sulfonamide | [NX3][CX3](=[OX1]).[SX4](=[OX1])(=[OX1])[NX3] | [NX3][CX3](=[OX1])[#6].[SX4](=[OX1])(=[OX1])[NX3] | [NX3][CX3](=[OX1])[#6].[S](=[OX1])(=[OX1])[NX3] | [NX3][CX3](=[OX1])[#6].[#16X4](=[OX1])(=[OX1])[#7X3] | [NX3][CX3](=[OX1])[#6].[SX4](=[OX1])(=[OX1])[NX3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
+      <c r="I66" s="6" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>amide | sulfonamide | [NX3][CX3](=[OX1]).[NX3][SX4](=[OX1])(=[OX1]) | sulfonamide | amide | amide | sulfonamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>[CX3](=O)[NX3].[SX4](=O)(=O)[NX3] | amide | sulfonamide | [NX3][CX3](=O)[#6] | [SX4](=O)(=O)[NX3] | [NX3][CX3](=O)[#6].[SX4](=O)(=O)[NX3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>amide | sulfonamide | [NX3][CX3](=[OX1])[#6].[#6][SX4](=[OX1])(=[OX1])[NX3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>[NX3][CX3](=[OX1]).[NX3][SX4](=[OX1])(=[OX1]) | [NX3][CX3](=O)[#6].[NX3][SX4](=[OX1])(=[OX1])[#6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>amide | sulfonamide | amide | sulfonamide | [CX3](=[OX1])[NX3].[SX4](=[OX1])(=[OX1])[NX3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>How many molecules contain both an amide and a sulfonamide?</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>[NX3][CX3](=[OX1]).[SX4](=[OX1])(=[OX1])[NX3] | amide | sulfonamide | [#6][CX3](=[OX1])[NX3].[SX4](=[OX1])(=[OX1])[NX3]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12115,391 +15146,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Question set</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Time of day</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Asked</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Mean s</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Median s</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Slowest s</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Cost $</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Bare: DeepSeek alone, first 11 chemistry questions (stopped; 120 s limit)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>chemistry</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>122.1</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>132.3</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.578</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Dataset A: pre-fetch off</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0.078</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Dataset B: pre-fetch on</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Dataset E: pre-fetch on, thinking off</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.083</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Chemistry C: pre-fetch off, no R/S tool (stopped after 16)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>chemistry</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>232.9</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.413</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Chemistry D: pre-fetch on, no R/S tool</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>chemistry</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>172.7</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0.351</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>R/S questions: R/S tool, pre-fetch on</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>chemistry</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>afternoon</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0.021</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>R/S questions: R/S tool, pre-fetch off</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>chemistry</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>afternoon</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Bare smoke test: 20 s time limit</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>chemistry</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>morning</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0.011</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/results/assistant_audit.xlsx
+++ b/results/assistant_audit.xlsx
@@ -15,8 +15,9 @@
     <sheet name="Stereo note A-B test" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Linker difference A-B test" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Pattern check A-B test" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Model history" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Development runs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Near-miss A-B test" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Model history" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Development runs" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -694,36 +695,48 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model history</t>
+          <t>Near-miss A-B test</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Earlier runs that chose DeepSeek: after and before the speed work, and two local models. Listed best first; the order the runs were made in is in results/assistant_model_trials.csv.</t>
+          <t>'What is the CB2 Ki of &lt;ligand&gt;?' for 20 standard cannabinoid ligands, answer key from PubChem's structure for each name matched to the recorded measurements (stereo ignored): 14 in the dataset, 4 with every measurement removed for disagreeing, 3 never measured (JWH-073 is JWH-018 with one carbon fewer). Without the changes the assistant answered 'not in data' for compounds that are there: names are stored for few molecules and with their punctuation ('Sr-144528'), and it gave up after a name search or wrote a SMILES from memory with a substituent misplaced. B compares names on letters and digits only, asks for a SMILES retry after an unknown name, and offers recorded molecules with the same formula or Tanimoto &gt;= 0.9 when a SMILES has no exact match. Round 2: 13/20 against 19/20, median 16.0 s against 11.3 s. The remaining miss (L-759,656) is the model's own memory: it recalls L-759,656 as L-759,633's structure, and in one run chose it after looking up the right one; both variants miss it. Near misses were offered for JWH-073 in every B run and rejected each time. Adopted.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Model history</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Earlier runs that chose DeepSeek: after and before the speed work, and two local models. Listed best first; the order the runs were made in is in results/assistant_model_trials.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Development runs</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Every exploratory run made while refining the assistant, labelled.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Every chemistry category cleared the 90% bar set before the runs, so no chemistry-specialist model is needed alongside DeepSeek; where it was slow or wrong, the fix was a tool, not a model.</t>
         </is>
@@ -735,6 +748,284 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Runs on</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Prompt profile</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Asked</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Mean s</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Median s</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Slowest s</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Cost $</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>DeepSeek, full profile, after the speed work</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>hosted</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>DeepSeek, full profile, before the speed work</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>hosted</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.179</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>DeepSeek, compact profile (control)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>hosted</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>201.2</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Gemma 4 26B, local, compact profile</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>gemma4:26b</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3 14B, local, compact profile</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>qwen3:14b</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>233.8</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14876,271 +15167,4110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Runs on</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Prompt profile</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>'What is the CB2 Ki of &lt;ligand&gt;?' for 20 standard cannabinoid ligands, answer key from PubChem's structure for each name matched to the recorded measurements (stereo ignored): 14 in the dataset, 4 with every measurement removed for disagreeing, 3 never measured (JWH-073 is JWH-018 with one carbon fewer). Without the changes the assistant answered 'not in data' for compounds that are there: names are stored for few molecules and with their punctuation ('Sr-144528'), and it gave up after a name search or wrote a SMILES from memory with a substituent misplaced. B compares names on letters and digits only, asks for a SMILES retry after an unknown name, and offers recorded molecules with the same formula or Tanimoto &gt;= 0.9 when a SMILES has no exact match. Round 2: 13/20 against 19/20, median 16.0 s against 11.3 s. The remaining miss (L-759,656) is the model's own memory: it recalls L-759,656 as L-759,633's structure, and in one run chose it after looking up the right one; both variants miss it. Near misses were offered for JWH-073 in every B run and rejected each time. Adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>By round and variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Asked</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Near misses shown</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Median s</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Mean s</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Median s</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Slowest s</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cost $</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>DeepSeek, full profile, after the speed work</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>hosted</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>DeepSeek, full profile, before the speed work</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>hosted</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>145.4</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.179</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>DeepSeek, compact profile (control)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>hosted</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>compact</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>201.2</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Gemma 4 26B, local, compact profile</t>
+          <t>1. All 20 questions: name matching, and near misses in lookup_compound</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>gemma4:26b</t>
+          <t>A: as before</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>compact</t>
-        </is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9</v>
+        <v>13.2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>18</v>
+        <v>26.7</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Qwen3 14B, local, compact profile</t>
+          <t>1. All 20 questions: name matching, and near misses in lookup_compound</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>qwen3:14b</t>
+          <t>B: name matching and near misses</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>compact</t>
-        </is>
+          <t>13/20</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.268</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2. All 20 questions: also near misses in describe_molecule, and a SMILES retry after an unknown name (adopted)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A: as before</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>13/20</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.414</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2. All 20 questions: also near misses in describe_molecule, and a SMILES retry after an unknown name (adopted)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>B: name matching and near misses</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>19/20</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.436</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>3. Q13 and Q19 three times: near misses report how their formula differs (adopted)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>B: name matching and near misses</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Every answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Near miss shown</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Tools used</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of SR144528 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, search_documents, get_document, query_table, query_table, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of WIN 55,212-2 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, describe_molecule, describe_molecule, search_documents, query_table, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CP 55,940 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, query_table, query_table, query_table, search_documents, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JTE-907 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM630 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>[7.443697499232712]</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM251 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>[6.958607314841775]</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>6.959</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, query_table, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-015 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>[7.651909206415738]</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>7.652</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, query_table, query_table, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of GW405833 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>[7.455931955649724, 8.161150909262744]</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>8.161</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, find_similar, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM1241 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>[8.04421089353657]</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>8.044</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, query_table, search_documents, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-018 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>[8.199970640755865]</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of A-836339 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>[9.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,633 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>[8.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, query_table, query_table, search_documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,656 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>[7.928117992693874]</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, search_documents, search_documents, search_documents, search_documents, search_documents, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-210 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>[9.161025045044532]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>9.161</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of BAY 59-3074 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>[7.341988603342887]</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, query_table, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of UR-144 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>[8.74232805345581]</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>8.742</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CB-13 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>[7.721246399047171]</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>7.721</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, lookup_compound, find_similar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>233.8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM-2201 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-073 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>query_table, query_table, lookup_compound, search_documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of XLR-11 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, lookup_compound, find_similar, query_table, query_table, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of SR144528 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound (pre-fetched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of WIN 55,212-2 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound (pre-fetched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CP 55,940 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound (pre-fetched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JTE-907 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, get_document, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM630 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>[7.443697499232712]</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM251 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>[6.958607314841775]</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, query_table, describe_molecule, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-015 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>[7.651909206415738]</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>7.652</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, lookup_compound, query_table, describe_molecule, query_table, query_table, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of GW405833 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>[7.455931955649724, 8.161150909262744]</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM1241 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>[8.04421089353657]</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>8.044</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, describe_molecule, find_similar, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-018 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>[8.199970640755865]</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, query_table, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of A-836339 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>[9.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,633 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>[8.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>8.194</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, describe_molecule, find_similar, query_table, describe_molecule, compare_molecules, lookup_compound, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,656 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>[7.928117992693874]</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>7.928</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, search_documents, query_table, describe_molecule, query_table, query_table, query_table, query_table, query_table, query_table, search_project, search_project, describe_molecule, query_table, lookup_compound, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-210 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>[9.161025045044532]</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>9.161</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of BAY 59-3074 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>[7.341988603342887]</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, query_table, get_document, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of UR-144 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>[8.74232805345581]</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>8.742</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, describe_molecule, find_similar, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CB-13 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>[7.721246399047171]</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, search_documents, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM-2201 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, describe_molecule, find_similar, query_table, query_table, search_documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-073 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, query_table, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of XLR-11 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of SR144528 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, query_table, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of WIN 55,212-2 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CP 55,940 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, query_table, search_documents, search_documents, lookup_compound, lookup_compound, describe_molecule, find_similar, describe_molecule, lookup_compound, query_table, query_table, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JTE-907 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, query_table, query_table, get_document</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM630 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>[7.443697499232712]</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, query_table, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM251 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>[6.958607314841775]</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>6.959</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
+      <c r="I58" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, search_documents, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-015 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>[7.651909206415738]</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>7.652</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, find_similar, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of GW405833 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>[7.455931955649724, 8.161150909262744]</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, query_table, get_document, get_document, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM1241 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>[8.04421089353657]</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>8.044</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-018 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>[8.199970640755865]</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of A-836339 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>[9.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,633 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>[8.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>8.194</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
+      <c r="I64" s="6" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, search_documents, query_table, describe_molecule, find_similar, lookup_compound, describe_molecule, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,656 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>[7.928117992693874]</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>8.194</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="n">
+        <v>219.2</v>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, search_documents, search_documents, query_table, query_table, query_table, describe_molecule, query_table, describe_molecule, query_table, query_table, query_table, query_table, describe_molecule, lookup_compound, describe_molecule, query_table, describe_molecule, query_table, query_table, query_table, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-210 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>[9.161025045044532]</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>9.161</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
+      <c r="I66" s="6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of BAY 59-3074 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>[7.341988603342887]</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>7.342</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, query_table, get_document, query_table, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of UR-144 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>[8.74232805345581]</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>8.742</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
+      <c r="I68" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CB-13 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>[7.721246399047171]</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>7.721</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr"/>
+      <c r="I69" s="6" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, describe_molecule, query_table, search_documents, search_documents, search_documents, get_document, query_table, query_table, query_table, query_table, query_table, find_similar, describe_molecule, lookup_compound, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM-2201 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
+      <c r="I70" s="6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, describe_molecule, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-073 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr"/>
+      <c r="I71" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, query_table, query_table, query_table, describe_molecule, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of XLR-11 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr"/>
+      <c r="I72" s="6" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, query_table, describe_molecule, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of SR144528 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr"/>
+      <c r="I73" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound (pre-fetched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of WIN 55,212-2 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
+      <c r="I74" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound (pre-fetched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CP 55,940 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr"/>
+      <c r="I75" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound (pre-fetched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JTE-907 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr"/>
+      <c r="I76" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM630 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>[7.443697499232712]</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>7.444</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr"/>
+      <c r="I77" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM251 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>[6.958607314841775]</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>6.959</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, lookup_compound, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-015 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>[7.651909206415738]</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>7.652</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr"/>
+      <c r="I79" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of GW405833 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>[7.455931955649724, 8.161150909262744]</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>8.161</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr"/>
+      <c r="I80" s="6" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, search_documents, get_document, query_table, lookup_compound, describe_molecule, query_table, query_table, lookup_compound, lookup_compound, get_document, get_document, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM1241 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>[8.04421089353657]</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>8.044</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, lookup_compound, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-018 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>[8.199970640755865]</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of A-836339 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>[9.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>9.194</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, lookup_compound, query_table, search_documents, find_similar, get_document, query_table, query_table, describe_molecule, lookup_compound, lookup_compound, describe_molecule, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,633 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>[8.193820026016112]</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>8.194</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, search_documents, search_documents, search_documents, search_documents, search_documents, search_documents, search_documents, query_table, query_table, query_table, describe_molecule, lookup_compound, describe_molecule, lookup_compound, query_table, query_table, describe_molecule, lookup_compound, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,656 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>[7.928117992693874]</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>8.194</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule, lookup_compound, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-210 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>[9.161025045044532]</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>9.161</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of BAY 59-3074 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>[7.341988603342887]</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>7.342</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr"/>
+      <c r="I87" s="6" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, query_table, get_document, query_table, lookup_compound, describe_molecule, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of UR-144 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>[8.74232805345581]</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>8.742</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr"/>
+      <c r="I88" s="6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of CB-13 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>[7.721246399047171]</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>7.721</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr"/>
+      <c r="I89" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>query_table, query_table, describe_molecule, search_documents, lookup_compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of AM-2201 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-073 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of XLR-11 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
+      <c r="I92" s="6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, lookup_compound, query_table, query_table, search_documents, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,656 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>[7.928117992693874]</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>8.194</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, search_documents, search_documents, describe_molecule, lookup_compound, lookup_compound, lookup_compound, lookup_compound, describe_molecule, draw_molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-073 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, lookup_compound, describe_molecule, query_table, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,656 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>[7.928117992693874]</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>7.928</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr"/>
+      <c r="I95" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, query_table, search_documents, search_documents, search_project, search_project, lookup_compound, describe_molecule</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-073 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, lookup_compound, describe_molecule, query_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of L-759,656 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>[7.928117992693874]</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>8.194</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, describe_molecule, query_table, describe_molecule, query_table, query_table, describe_molecule, describe_molecule, lookup_compound, lookup_compound, get_document, search_documents, search_documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>What is the CB2 Ki of JWH-073 in this dataset?</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>NOT IN DATA</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>lookup_compound, describe_molecule</t>
+        </is>
       </c>
     </row>
   </sheetData>
